--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_monsterPoint.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_monsterPoint.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_monsterPoint" sheetId="1" r:id="rId1"/>
@@ -3839,7 +3839,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -3866,7 +3866,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -3893,7 +3893,7 @@
         <v>23</v>
       </c>
       <c r="E7" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>23</v>
       </c>
       <c r="E8" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>23</v>
       </c>
       <c r="E9" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>23</v>
       </c>
       <c r="E10" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -4001,7 +4001,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -4028,7 +4028,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>23</v>
       </c>
       <c r="E13" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>23</v>
       </c>
       <c r="E14" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>35</v>
       </c>
       <c r="E15" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -4135,8 +4135,8 @@
       <c r="D16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="1">
-        <v>4</v>
+      <c r="E16" s="8">
+        <v>5</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>35</v>
       </c>
       <c r="E17" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -4189,8 +4189,8 @@
       <c r="D18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="1">
-        <v>4</v>
+      <c r="E18" s="8">
+        <v>5</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -4217,7 +4217,7 @@
         <v>35</v>
       </c>
       <c r="E19" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -4243,8 +4243,8 @@
       <c r="D20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="1">
-        <v>4</v>
+      <c r="E20" s="8">
+        <v>5</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -4271,7 +4271,7 @@
         <v>35</v>
       </c>
       <c r="E21" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -4297,8 +4297,8 @@
       <c r="D22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="1">
-        <v>4</v>
+      <c r="E22" s="8">
+        <v>5</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>35</v>
       </c>
       <c r="E23" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>35</v>
       </c>
       <c r="E24" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>46</v>
       </c>
       <c r="E25" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -4406,7 +4406,7 @@
         <v>46</v>
       </c>
       <c r="E26" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -4433,7 +4433,7 @@
         <v>46</v>
       </c>
       <c r="E27" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>46</v>
       </c>
       <c r="E28" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -4514,7 +4514,7 @@
         <v>46</v>
       </c>
       <c r="E30" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -4541,7 +4541,7 @@
         <v>46</v>
       </c>
       <c r="E31" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>46</v>
       </c>
       <c r="E32" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>55</v>
       </c>
       <c r="E33" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>55</v>
       </c>
       <c r="E34" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>55</v>
       </c>
       <c r="E35" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>55</v>
       </c>
       <c r="E36" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         <v>55</v>
       </c>
       <c r="E37" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>55</v>
       </c>
       <c r="E38" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>55</v>
       </c>
       <c r="E39" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         <v>55</v>
       </c>
       <c r="E40" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -5027,7 +5027,7 @@
         <v>73</v>
       </c>
       <c r="E49" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>73</v>
       </c>
       <c r="E50" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>73</v>
       </c>
       <c r="E51" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -5108,7 +5108,7 @@
         <v>73</v>
       </c>
       <c r="E52" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -5135,7 +5135,7 @@
         <v>73</v>
       </c>
       <c r="E53" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>73</v>
       </c>
       <c r="E54" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         <v>73</v>
       </c>
       <c r="E55" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         <v>73</v>
       </c>
       <c r="E56" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -5459,7 +5459,7 @@
         <v>91</v>
       </c>
       <c r="E65" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -5486,7 +5486,7 @@
         <v>91</v>
       </c>
       <c r="E66" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         <v>91</v>
       </c>
       <c r="E67" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>91</v>
       </c>
       <c r="E68" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>91</v>
       </c>
       <c r="E69" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -5594,7 +5594,7 @@
         <v>91</v>
       </c>
       <c r="E70" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -5621,7 +5621,7 @@
         <v>91</v>
       </c>
       <c r="E71" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>100</v>
       </c>
       <c r="E73" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>100</v>
       </c>
       <c r="E74" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -5729,7 +5729,7 @@
         <v>100</v>
       </c>
       <c r="E75" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -5756,7 +5756,7 @@
         <v>100</v>
       </c>
       <c r="E76" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -5783,7 +5783,7 @@
         <v>100</v>
       </c>
       <c r="E77" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -5810,7 +5810,7 @@
         <v>100</v>
       </c>
       <c r="E78" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -5837,7 +5837,7 @@
         <v>100</v>
       </c>
       <c r="E79" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -5864,7 +5864,7 @@
         <v>100</v>
       </c>
       <c r="E80" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -5891,7 +5891,7 @@
         <v>109</v>
       </c>
       <c r="E81" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>109</v>
       </c>
       <c r="E82" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -5945,7 +5945,7 @@
         <v>109</v>
       </c>
       <c r="E83" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -5972,7 +5972,7 @@
         <v>109</v>
       </c>
       <c r="E84" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         <v>109</v>
       </c>
       <c r="E85" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -6026,7 +6026,7 @@
         <v>109</v>
       </c>
       <c r="E86" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>109</v>
       </c>
       <c r="E87" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -6080,7 +6080,7 @@
         <v>109</v>
       </c>
       <c r="E88" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>118</v>
       </c>
       <c r="E89" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -6134,7 +6134,7 @@
         <v>118</v>
       </c>
       <c r="E90" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>118</v>
       </c>
       <c r="E91" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>118</v>
       </c>
       <c r="E92" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -6215,7 +6215,7 @@
         <v>118</v>
       </c>
       <c r="E93" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         <v>118</v>
       </c>
       <c r="E94" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -6269,7 +6269,7 @@
         <v>125</v>
       </c>
       <c r="E95" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         <v>139</v>
       </c>
       <c r="E111" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -7457,7 +7457,7 @@
         <v>177</v>
       </c>
       <c r="E139" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
@@ -7484,7 +7484,7 @@
         <v>177</v>
       </c>
       <c r="E140" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>177</v>
       </c>
       <c r="E141" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -7538,7 +7538,7 @@
         <v>177</v>
       </c>
       <c r="E142" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7565,7 +7565,7 @@
         <v>177</v>
       </c>
       <c r="E143" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>183</v>
       </c>
       <c r="E144" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>183</v>
       </c>
       <c r="E146" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>201</v>
       </c>
       <c r="E163" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1">
         <v>0</v>
@@ -8321,7 +8321,7 @@
         <v>212</v>
       </c>
       <c r="E171" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F171" s="1">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>282</v>
       </c>
       <c r="E232" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F232" s="1">
         <v>0</v>
@@ -10292,7 +10292,7 @@
         <v>286</v>
       </c>
       <c r="E244" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F244" s="1">
         <v>0</v>
@@ -11237,7 +11237,7 @@
         <v>320</v>
       </c>
       <c r="E279" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F279" s="1">
         <v>0</v>
@@ -11804,7 +11804,7 @@
         <v>323</v>
       </c>
       <c r="E300" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F300" s="1">
         <v>0</v>
@@ -11993,7 +11993,7 @@
         <v>330</v>
       </c>
       <c r="E307" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F307" s="1">
         <v>0</v>
@@ -12128,7 +12128,7 @@
         <v>335</v>
       </c>
       <c r="E312" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F312" s="1">
         <v>0</v>
@@ -12587,7 +12587,7 @@
         <v>342</v>
       </c>
       <c r="E329" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F329" s="1">
         <v>0</v>
@@ -12641,7 +12641,7 @@
         <v>344</v>
       </c>
       <c r="E331" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F331" s="1">
         <v>0</v>
@@ -12668,7 +12668,7 @@
         <v>344</v>
       </c>
       <c r="E332" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1">
         <v>0</v>
@@ -12695,7 +12695,7 @@
         <v>344</v>
       </c>
       <c r="E333" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F333" s="1">
         <v>0</v>
@@ -12722,7 +12722,7 @@
         <v>344</v>
       </c>
       <c r="E334" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F334" s="1">
         <v>0</v>
@@ -12749,7 +12749,7 @@
         <v>344</v>
       </c>
       <c r="E335" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F335" s="1">
         <v>0</v>
@@ -12776,7 +12776,7 @@
         <v>344</v>
       </c>
       <c r="E336" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F336" s="1">
         <v>0</v>
@@ -12857,7 +12857,7 @@
         <v>351</v>
       </c>
       <c r="E339" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1">
         <v>0</v>
@@ -12911,7 +12911,7 @@
         <v>351</v>
       </c>
       <c r="E341" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F341" s="1">
         <v>0</v>
@@ -13343,7 +13343,7 @@
         <v>368</v>
       </c>
       <c r="E357" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F357" s="1">
         <v>0</v>
@@ -13748,7 +13748,7 @@
         <v>371</v>
       </c>
       <c r="E372" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F372" s="1">
         <v>0</v>
@@ -13991,7 +13991,7 @@
         <v>379</v>
       </c>
       <c r="E381" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F381" s="1">
         <v>0</v>
@@ -14153,7 +14153,7 @@
         <v>385</v>
       </c>
       <c r="E387" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F387" s="1">
         <v>0</v>
@@ -14504,7 +14504,7 @@
         <v>402</v>
       </c>
       <c r="E400" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F400" s="1">
         <v>0</v>
@@ -14839,7 +14839,7 @@
         <v>417</v>
       </c>
       <c r="E412" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F412" s="1">
         <v>0</v>
@@ -15007,7 +15007,7 @@
         <v>429</v>
       </c>
       <c r="E418" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F418" s="1">
         <v>0</v>
@@ -15035,7 +15035,7 @@
         <v>429</v>
       </c>
       <c r="E419" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F419" s="1">
         <v>0</v>
@@ -15063,7 +15063,7 @@
         <v>429</v>
       </c>
       <c r="E420" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F420" s="1">
         <v>0</v>
@@ -15343,7 +15343,7 @@
         <v>442</v>
       </c>
       <c r="E430" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F430" s="1">
         <v>0</v>
@@ -15371,7 +15371,7 @@
         <v>444</v>
       </c>
       <c r="E431" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F431" s="1">
         <v>0</v>
@@ -15539,7 +15539,7 @@
         <v>451</v>
       </c>
       <c r="E437" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F437" s="1">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>451</v>
       </c>
       <c r="E438" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F438" s="1">
         <v>0</v>
@@ -15791,7 +15791,7 @@
         <v>373</v>
       </c>
       <c r="E446" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F446" s="1">
         <v>0</v>
@@ -15819,7 +15819,7 @@
         <v>373</v>
       </c>
       <c r="E447" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F447" s="1">
         <v>0</v>
@@ -16603,7 +16603,7 @@
         <v>489</v>
       </c>
       <c r="E475" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F475" s="1">
         <v>0</v>
@@ -16659,7 +16659,7 @@
         <v>489</v>
       </c>
       <c r="E477" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F477" s="1">
         <v>0</v>
@@ -16883,7 +16883,7 @@
         <v>46</v>
       </c>
       <c r="E485" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F485" s="1">
         <v>0</v>
@@ -16995,7 +16995,7 @@
         <v>494</v>
       </c>
       <c r="E489" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F489" s="1">
         <v>0</v>
@@ -17219,7 +17219,7 @@
         <v>510</v>
       </c>
       <c r="E497" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F497" s="1">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>510</v>
       </c>
       <c r="E498" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F498" s="1">
         <v>0</v>
@@ -17303,7 +17303,7 @@
         <v>510</v>
       </c>
       <c r="E500" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F500" s="1">
         <v>0</v>
@@ -18479,7 +18479,7 @@
         <v>561</v>
       </c>
       <c r="E542" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F542" s="1">
         <v>0</v>
@@ -18675,7 +18675,7 @@
         <v>569</v>
       </c>
       <c r="E549" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F549" s="1">
         <v>0</v>
@@ -18703,7 +18703,7 @@
         <v>569</v>
       </c>
       <c r="E550" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F550" s="1">
         <v>0</v>
@@ -18899,7 +18899,7 @@
         <v>578</v>
       </c>
       <c r="E557" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F557" s="1">
         <v>0</v>
@@ -18930,7 +18930,7 @@
         <v>578</v>
       </c>
       <c r="E558" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F558" s="1">
         <v>0</v>
@@ -19178,7 +19178,7 @@
         <v>588</v>
       </c>
       <c r="E566" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F566" s="1">
         <v>0</v>
@@ -19209,7 +19209,7 @@
         <v>588</v>
       </c>
       <c r="E567" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F567" s="1">
         <v>0</v>
@@ -19643,7 +19643,7 @@
         <v>605</v>
       </c>
       <c r="E581" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F581" s="1">
         <v>0</v>
@@ -19674,7 +19674,7 @@
         <v>605</v>
       </c>
       <c r="E582" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F582" s="1">
         <v>0</v>
@@ -19705,7 +19705,7 @@
         <v>605</v>
       </c>
       <c r="E583" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F583" s="1">
         <v>0</v>
@@ -19922,7 +19922,7 @@
         <v>605</v>
       </c>
       <c r="E590" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F590" s="1">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         <v>605</v>
       </c>
       <c r="E591" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F591" s="1">
         <v>0</v>
@@ -19984,7 +19984,7 @@
         <v>605</v>
       </c>
       <c r="E592" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F592" s="1">
         <v>0</v>
@@ -22466,7 +22466,7 @@
         <v>721</v>
       </c>
       <c r="E686" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F686" s="1">
         <v>0</v>
@@ -22489,7 +22489,7 @@
         <v>723</v>
       </c>
       <c r="E687" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F687" s="1">
         <v>0</v>
@@ -22512,7 +22512,7 @@
         <v>721</v>
       </c>
       <c r="E688" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F688" s="1">
         <v>0</v>
@@ -22535,7 +22535,7 @@
         <v>723</v>
       </c>
       <c r="E689" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F689" s="1">
         <v>0</v>
@@ -22558,7 +22558,7 @@
         <v>721</v>
       </c>
       <c r="E690" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F690" s="1">
         <v>0</v>
@@ -22581,7 +22581,7 @@
         <v>723</v>
       </c>
       <c r="E691" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F691" s="1">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>721</v>
       </c>
       <c r="E692" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F692" s="1">
         <v>0</v>
@@ -22627,7 +22627,7 @@
         <v>723</v>
       </c>
       <c r="E693" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F693" s="1">
         <v>0</v>
@@ -22650,7 +22650,7 @@
         <v>721</v>
       </c>
       <c r="E694" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F694" s="1">
         <v>0</v>
@@ -22673,7 +22673,7 @@
         <v>723</v>
       </c>
       <c r="E695" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F695" s="1">
         <v>0</v>
@@ -22696,7 +22696,7 @@
         <v>721</v>
       </c>
       <c r="E696" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F696" s="1">
         <v>0</v>
@@ -22719,7 +22719,7 @@
         <v>723</v>
       </c>
       <c r="E697" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F697" s="1">
         <v>0</v>
@@ -22742,7 +22742,7 @@
         <v>721</v>
       </c>
       <c r="E698" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F698" s="1">
         <v>0</v>
@@ -22765,7 +22765,7 @@
         <v>723</v>
       </c>
       <c r="E699" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F699" s="1">
         <v>0</v>
@@ -22788,7 +22788,7 @@
         <v>721</v>
       </c>
       <c r="E700" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F700" s="1">
         <v>0</v>
@@ -22811,7 +22811,7 @@
         <v>723</v>
       </c>
       <c r="E701" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F701" s="1">
         <v>0</v>
@@ -22834,7 +22834,7 @@
         <v>721</v>
       </c>
       <c r="E702" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F702" s="1">
         <v>0</v>
@@ -22857,7 +22857,7 @@
         <v>723</v>
       </c>
       <c r="E703" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F703" s="1">
         <v>0</v>
@@ -22880,7 +22880,7 @@
         <v>721</v>
       </c>
       <c r="E704" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F704" s="1">
         <v>0</v>
@@ -22903,7 +22903,7 @@
         <v>723</v>
       </c>
       <c r="E705" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F705" s="1">
         <v>0</v>
@@ -22926,7 +22926,7 @@
         <v>721</v>
       </c>
       <c r="E706" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F706" s="1">
         <v>0</v>
@@ -22949,7 +22949,7 @@
         <v>723</v>
       </c>
       <c r="E707" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F707" s="1">
         <v>0</v>
@@ -23248,7 +23248,7 @@
         <v>721</v>
       </c>
       <c r="E720" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F720" s="1">
         <v>0</v>
@@ -23271,7 +23271,7 @@
         <v>723</v>
       </c>
       <c r="E721" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F721" s="1">
         <v>0</v>
@@ -23294,7 +23294,7 @@
         <v>721</v>
       </c>
       <c r="E722" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F722" s="1">
         <v>0</v>
@@ -23317,7 +23317,7 @@
         <v>723</v>
       </c>
       <c r="E723" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F723" s="1">
         <v>0</v>
@@ -24544,7 +24544,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C519:C521 C523:C525 C503:C515 E453:E502 E1:E445 C528:C558 C566:C592">
+  <conditionalFormatting sqref="E1:E445 E453:E502 C503:C515 C519:C521 C523:C525 C528:C558 C566:C592">
     <cfRule type="cellIs" dxfId="0" priority="51" operator="equal">
       <formula>1</formula>
     </cfRule>
